--- a/anomaly_detection_metrics/hbw_1_metrics_table.xlsx
+++ b/anomaly_detection_metrics/hbw_1_metrics_table.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8378112712975099</v>
+        <v>0.7949273120940303</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6627338129496403</v>
+        <v>0.6610999136193493</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5703551912568307</v>
+        <v>0.5702272727272727</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9887857695282289</v>
+        <v>0.9938128383604021</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8905645784996133</v>
+        <v>0.8878576952822892</v>
       </c>
       <c r="D3" t="n">
-        <v>0.968677494199536</v>
+        <v>0.9702242846094354</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9070592408655552</v>
+        <v>0.8833132840694278</v>
       </c>
       <c r="C4" t="n">
-        <v>0.759940603860749</v>
+        <v>0.7578808384221818</v>
       </c>
       <c r="D4" t="n">
-        <v>0.717970765262253</v>
+        <v>0.7182937303177784</v>
       </c>
     </row>
     <row r="5">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9543893699611825</v>
+        <v>0.9464535611696251</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8332730298863884</v>
+        <v>0.8308605341246289</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8499592833876223</v>
+        <v>0.8508545849158979</v>
       </c>
     </row>
     <row r="6">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08585121482610703</v>
+        <v>0.07076617330312729</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
